--- a/healthcare_surveys/042_hospital_environment_feedback_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/042_hospital_environment_feedback_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Select Facilities Option</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleanliness</t>
+          <t>Select Cleanliness Option</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Select Parking Option</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Waiting Time</t>
+          <t>Select Waiting Time Option</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Communication Effectiveness</t>
+          <t>Select Communication Effectiveness Option</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1043,8 +1043,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Very Poor', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Very Poor', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Very Poor', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Very Poor', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor', 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Very Poor', 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
